--- a/3. G_Documents/2. Products_Firmware/VNSH02_C43/BOX_Camera.xlsx
+++ b/3. G_Documents/2. Products_Firmware/VNSH02_C43/BOX_Camera.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\3. G_Documents\2. Products_Firmware\VNSH02_C43\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67888375-492D-45BD-A336-4474941D66E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000CD24D-DB58-4116-9F8C-EA5692A82DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4530" yWindow="4365" windowWidth="21600" windowHeight="11835" xr2:uid="{817CF325-9735-4180-B807-100625816377}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{817CF325-9735-4180-B807-100625816377}"/>
   </bookViews>
   <sheets>
     <sheet name="BOX_Camera" sheetId="1" r:id="rId1"/>
@@ -106,12 +106,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF081B3A"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -121,6 +115,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF081B3A"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -168,10 +168,10 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -494,18 +494,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -593,7 +593,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>